--- a/artfynd/A 36622-2024 artfynd.xlsx
+++ b/artfynd/A 36622-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120229579</v>
+        <v>120229575</v>
       </c>
       <c r="B2" t="n">
-        <v>100171</v>
+        <v>100194</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>656876</v>
+        <v>656870</v>
       </c>
       <c r="R2" t="n">
-        <v>6680021</v>
+        <v>6680030</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120229575</v>
+        <v>120229571</v>
       </c>
       <c r="B3" t="n">
-        <v>100171</v>
+        <v>100194</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -831,14 +831,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hällsmyren, Upl</t>
+          <t>Storslätten, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>656870</v>
+        <v>657120</v>
       </c>
       <c r="R3" t="n">
-        <v>6680030</v>
+        <v>6679844</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120229590</v>
+        <v>120229579</v>
       </c>
       <c r="B4" t="n">
-        <v>100171</v>
+        <v>100194</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>656910</v>
+        <v>656876</v>
       </c>
       <c r="R4" t="n">
-        <v>6680007</v>
+        <v>6680021</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -986,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120229585</v>
+        <v>120229590</v>
       </c>
       <c r="B5" t="n">
-        <v>100171</v>
+        <v>100194</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1067,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>656905</v>
+        <v>656910</v>
       </c>
       <c r="R5" t="n">
-        <v>6680005</v>
+        <v>6680007</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120229571</v>
+        <v>120229585</v>
       </c>
       <c r="B6" t="n">
-        <v>100171</v>
+        <v>100194</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1179,14 +1179,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Storslätten, Upl</t>
+          <t>Hällsmyren, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>657120</v>
+        <v>656905</v>
       </c>
       <c r="R6" t="n">
-        <v>6679844</v>
+        <v>6680005</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 36622-2024 artfynd.xlsx
+++ b/artfynd/A 36622-2024 artfynd.xlsx
@@ -791,7 +791,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120229571</v>
+        <v>120229579</v>
       </c>
       <c r="B3" t="n">
         <v>100194</v>
@@ -831,14 +831,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Storslätten, Upl</t>
+          <t>Hällsmyren, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>657120</v>
+        <v>656876</v>
       </c>
       <c r="R3" t="n">
-        <v>6679844</v>
+        <v>6680021</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,7 +907,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120229579</v>
+        <v>120229590</v>
       </c>
       <c r="B4" t="n">
         <v>100194</v>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>656876</v>
+        <v>656910</v>
       </c>
       <c r="R4" t="n">
-        <v>6680021</v>
+        <v>6680007</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -986,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,7 +1023,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120229590</v>
+        <v>120229585</v>
       </c>
       <c r="B5" t="n">
         <v>100194</v>
@@ -1067,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>656910</v>
+        <v>656905</v>
       </c>
       <c r="R5" t="n">
-        <v>6680007</v>
+        <v>6680005</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,7 +1139,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120229585</v>
+        <v>120229571</v>
       </c>
       <c r="B6" t="n">
         <v>100194</v>
@@ -1179,14 +1179,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hällsmyren, Upl</t>
+          <t>Storslätten, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>656905</v>
+        <v>657120</v>
       </c>
       <c r="R6" t="n">
-        <v>6680005</v>
+        <v>6679844</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 36622-2024 artfynd.xlsx
+++ b/artfynd/A 36622-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120229575</v>
+        <v>120229590</v>
       </c>
       <c r="B2" t="n">
         <v>100194</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>656870</v>
+        <v>656910</v>
       </c>
       <c r="R2" t="n">
-        <v>6680030</v>
+        <v>6680007</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,7 +791,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120229579</v>
+        <v>120229575</v>
       </c>
       <c r="B3" t="n">
         <v>100194</v>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>656876</v>
+        <v>656870</v>
       </c>
       <c r="R3" t="n">
-        <v>6680021</v>
+        <v>6680030</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,7 +907,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120229590</v>
+        <v>120229585</v>
       </c>
       <c r="B4" t="n">
         <v>100194</v>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>656910</v>
+        <v>656905</v>
       </c>
       <c r="R4" t="n">
-        <v>6680007</v>
+        <v>6680005</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -986,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,7 +1023,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120229585</v>
+        <v>120229579</v>
       </c>
       <c r="B5" t="n">
         <v>100194</v>
@@ -1067,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>656905</v>
+        <v>656876</v>
       </c>
       <c r="R5" t="n">
-        <v>6680005</v>
+        <v>6680021</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 36622-2024 artfynd.xlsx
+++ b/artfynd/A 36622-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120229590</v>
+        <v>120229571</v>
       </c>
       <c r="B2" t="n">
         <v>100194</v>
@@ -715,14 +715,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hällsmyren, Upl</t>
+          <t>Storslätten, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>656910</v>
+        <v>657120</v>
       </c>
       <c r="R2" t="n">
-        <v>6680007</v>
+        <v>6679844</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,7 +791,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120229575</v>
+        <v>120229585</v>
       </c>
       <c r="B3" t="n">
         <v>100194</v>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>656870</v>
+        <v>656905</v>
       </c>
       <c r="R3" t="n">
-        <v>6680030</v>
+        <v>6680005</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,7 +907,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120229585</v>
+        <v>120229579</v>
       </c>
       <c r="B4" t="n">
         <v>100194</v>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>656905</v>
+        <v>656876</v>
       </c>
       <c r="R4" t="n">
-        <v>6680005</v>
+        <v>6680021</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -986,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,7 +1023,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120229579</v>
+        <v>120229575</v>
       </c>
       <c r="B5" t="n">
         <v>100194</v>
@@ -1067,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>656876</v>
+        <v>656870</v>
       </c>
       <c r="R5" t="n">
-        <v>6680021</v>
+        <v>6680030</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,7 +1139,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120229571</v>
+        <v>120229590</v>
       </c>
       <c r="B6" t="n">
         <v>100194</v>
@@ -1179,14 +1179,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Storslätten, Upl</t>
+          <t>Hällsmyren, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>657120</v>
+        <v>656910</v>
       </c>
       <c r="R6" t="n">
-        <v>6679844</v>
+        <v>6680007</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 36622-2024 artfynd.xlsx
+++ b/artfynd/A 36622-2024 artfynd.xlsx
@@ -791,7 +791,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120229585</v>
+        <v>120229590</v>
       </c>
       <c r="B3" t="n">
         <v>100194</v>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>656905</v>
+        <v>656910</v>
       </c>
       <c r="R3" t="n">
-        <v>6680005</v>
+        <v>6680007</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,7 +907,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120229579</v>
+        <v>120229585</v>
       </c>
       <c r="B4" t="n">
         <v>100194</v>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>656876</v>
+        <v>656905</v>
       </c>
       <c r="R4" t="n">
-        <v>6680021</v>
+        <v>6680005</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -986,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,7 +1023,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120229575</v>
+        <v>120229579</v>
       </c>
       <c r="B5" t="n">
         <v>100194</v>
@@ -1067,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>656870</v>
+        <v>656876</v>
       </c>
       <c r="R5" t="n">
-        <v>6680030</v>
+        <v>6680021</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,7 +1139,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120229590</v>
+        <v>120229575</v>
       </c>
       <c r="B6" t="n">
         <v>100194</v>
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>656910</v>
+        <v>656870</v>
       </c>
       <c r="R6" t="n">
-        <v>6680007</v>
+        <v>6680030</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 36622-2024 artfynd.xlsx
+++ b/artfynd/A 36622-2024 artfynd.xlsx
@@ -791,7 +791,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120229590</v>
+        <v>120229575</v>
       </c>
       <c r="B3" t="n">
         <v>100194</v>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>656910</v>
+        <v>656870</v>
       </c>
       <c r="R3" t="n">
-        <v>6680007</v>
+        <v>6680030</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,7 +907,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120229585</v>
+        <v>120229579</v>
       </c>
       <c r="B4" t="n">
         <v>100194</v>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>656905</v>
+        <v>656876</v>
       </c>
       <c r="R4" t="n">
-        <v>6680005</v>
+        <v>6680021</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -986,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,7 +1023,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120229579</v>
+        <v>120229590</v>
       </c>
       <c r="B5" t="n">
         <v>100194</v>
@@ -1067,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>656876</v>
+        <v>656910</v>
       </c>
       <c r="R5" t="n">
-        <v>6680021</v>
+        <v>6680007</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,7 +1139,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120229575</v>
+        <v>120229585</v>
       </c>
       <c r="B6" t="n">
         <v>100194</v>
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>656870</v>
+        <v>656905</v>
       </c>
       <c r="R6" t="n">
-        <v>6680030</v>
+        <v>6680005</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 36622-2024 artfynd.xlsx
+++ b/artfynd/A 36622-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120229571</v>
+        <v>120229585</v>
       </c>
       <c r="B2" t="n">
         <v>100194</v>
@@ -715,14 +715,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Storslätten, Upl</t>
+          <t>Hällsmyren, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>657120</v>
+        <v>656905</v>
       </c>
       <c r="R2" t="n">
-        <v>6679844</v>
+        <v>6680005</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,7 +791,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120229575</v>
+        <v>120229590</v>
       </c>
       <c r="B3" t="n">
         <v>100194</v>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>656870</v>
+        <v>656910</v>
       </c>
       <c r="R3" t="n">
-        <v>6680030</v>
+        <v>6680007</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1023,7 +1023,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120229590</v>
+        <v>120229575</v>
       </c>
       <c r="B5" t="n">
         <v>100194</v>
@@ -1067,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>656910</v>
+        <v>656870</v>
       </c>
       <c r="R5" t="n">
-        <v>6680007</v>
+        <v>6680030</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,7 +1139,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120229585</v>
+        <v>120229571</v>
       </c>
       <c r="B6" t="n">
         <v>100194</v>
@@ -1179,14 +1179,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hällsmyren, Upl</t>
+          <t>Storslätten, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>656905</v>
+        <v>657120</v>
       </c>
       <c r="R6" t="n">
-        <v>6680005</v>
+        <v>6679844</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
